--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/09_Anotacijos_logai/09_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/09_Anotacijos_logai/09_Anotavimo_logas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\09_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1188B6BF-94C8-44C1-879E-DECFC2B63443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A7166E-8DFE-4C86-8686-CC5F9F7F0A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="logas" sheetId="2" r:id="rId1"/>
@@ -293,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -320,7 +320,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -329,7 +329,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -618,7 +617,7 @@
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.90625" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" customWidth="1"/>
     <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.36328125" customWidth="1"/>
     <col min="6" max="6" width="32.90625" bestFit="1" customWidth="1"/>
@@ -694,7 +693,7 @@
       <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="b">
+      <c r="F2" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -703,7 +702,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="13" t="s">
         <v>3</v>
       </c>
       <c r="L2" t="s">
@@ -730,7 +729,7 @@
       <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4" t="b">
+      <c r="F3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -739,7 +738,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="13" t="s">
         <v>7</v>
       </c>
       <c r="L3" t="s">
@@ -764,7 +763,7 @@
       <c r="D4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="4" t="b">
+      <c r="F4" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -773,7 +772,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="14"/>
+      <c r="K4" s="13"/>
       <c r="L4" t="s">
         <v>8</v>
       </c>
@@ -796,7 +795,7 @@
       <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="b">
+      <c r="F5" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -805,7 +804,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="13" t="s">
         <v>12</v>
       </c>
       <c r="L5" t="s">
@@ -830,14 +829,14 @@
       <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4" t="b">
+      <c r="F6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="13" t="s">
         <v>15</v>
       </c>
       <c r="L6" t="s">
@@ -862,14 +861,14 @@
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="b">
+      <c r="F7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="13" t="s">
         <v>15</v>
       </c>
       <c r="L7" t="s">
@@ -894,14 +893,14 @@
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="b">
+      <c r="F8" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="13" t="s">
         <v>15</v>
       </c>
       <c r="L8" t="s">
@@ -919,13 +918,13 @@
       <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="4" t="b">
+      <c r="F9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -939,13 +938,13 @@
       <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="4" t="b">
+      <c r="F10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -961,13 +960,13 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="b">
+      <c r="F11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="8"/>

--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/09_Anotacijos_logai/09_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/09_Anotacijos_logai/09_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\09_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A7166E-8DFE-4C86-8686-CC5F9F7F0A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF394C77-AE28-4C97-9F28-62F63A32802A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>basename</t>
   </si>
@@ -164,7 +164,13 @@
     <t>1630762.894</t>
   </si>
   <si>
-    <t>???</t>
+    <t>būtų galima žymėti ir triukšmus, nes didelė dalis geros kokybės įrašas (1111),</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ir daug ektopinių pūpsnių, bet tada reikia pažymėti ilgą gabalą, kaip triukšmingą, pradžioje,</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dar reikia pasvarstyti, ar verta</t>
   </si>
 </sst>
 </file>
@@ -612,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -699,7 +705,9 @@
       <c r="G2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="13" t="s">
@@ -735,7 +743,9 @@
       <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="13" t="s">
@@ -769,7 +779,9 @@
       <c r="G4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
@@ -801,7 +813,9 @@
       <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="13" t="s">
@@ -930,7 +944,9 @@
       <c r="G9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="8"/>
+      <c r="H9" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
     </row>
@@ -950,11 +966,14 @@
       <c r="G10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>42</v>
+      <c r="H10" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
+      <c r="N10" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -973,6 +992,14 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
+      <c r="N11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="N12" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>

--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/09_Anotacijos_logai/09_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/09_Anotacijos_logai/09_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\09_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF394C77-AE28-4C97-9F28-62F63A32802A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9340D20B-B994-40A2-9FF3-7770663E4ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -705,10 +705,9 @@
       <c r="G2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J2" s="4"/>
       <c r="K2" s="13" t="s">
         <v>3</v>
@@ -743,10 +742,10 @@
       <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J3" s="4"/>
       <c r="K3" s="13" t="s">
         <v>7</v>
@@ -779,10 +778,9 @@
       <c r="G4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="13"/>
       <c r="L4" t="s">
@@ -813,10 +811,9 @@
       <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="13" t="s">
         <v>12</v>
@@ -944,10 +941,9 @@
       <c r="G9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="8"/>
+      <c r="I9" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
@@ -966,10 +962,9 @@
       <c r="G10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="8"/>
+      <c r="I10" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J10" s="8"/>
       <c r="N10" t="s">
         <v>42</v>
